--- a/test/excel/links/written/refresh-error.xlsx
+++ b/test/excel/links/written/refresh-error.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fsave-23390/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fsave-39313/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0797E9AA-4FD3-174F-B57B-6F37CBA8DDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97A67E89-33EB-2146-80CD-18F07D860F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/test/excel/links/written/refresh-error.xlsx
+++ b/test/excel/links/written/refresh-error.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fsave-39313/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fsave-51168/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97A67E89-33EB-2146-80CD-18F07D860F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D827DD50-010D-0748-B729-BA2FDF251038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
